--- a/backtest_runs/20260410_193731/by_symbol/LSEVL/LSEVL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/LSEVL/LSEVL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-1323.539999999998</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>98676.46000000001</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98676.46000000001</v>
@@ -679,7 +679,7 @@
         <v>-12058.91999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>86617.54000000001</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>88676.38</v>
@@ -909,7 +909,7 @@
         <v>-2794.140000000006</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>91911.7</v>
@@ -1001,7 +1001,7 @@
         <v>-1764.720000000002</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>90588.16</v>
@@ -1185,7 +1185,7 @@
         <v>-2794.139999999993</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>99411.76000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-2647.080000000009</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>96764.68000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-147.0599999999969</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>100882.36</v>
@@ -1415,7 +1415,7 @@
         <v>-2794.139999999993</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100588.24</v>
@@ -1645,7 +1645,7 @@
         <v>-7794.17999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>105588.28</v>
